--- a/www/flightdata/xlsx/eoss-385.xlsx
+++ b/www/flightdata/xlsx/eoss-385.xlsx
@@ -2808,7 +2808,7 @@
         <v>29202.58</v>
       </c>
       <c r="I2">
-        <v>521</v>
+        <v>331</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
